--- a/data/trans_bre/P20B-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P20B-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-63,17; -8,3</t>
+          <t>-55,67; -8,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-48,01; 2,75</t>
+          <t>-49,26; 4,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-45,54; 8,22</t>
+          <t>-46,21; 6,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-37,15; 16,26</t>
+          <t>-43,41; 15,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-73,72; 10,51</t>
+          <t>-72,87; 12,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-84,02; 69,73</t>
+          <t>-87,19; 56,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-87,39; —</t>
+          <t>-90,98; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 16,3</t>
+          <t>-21,35; 16,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 14,41</t>
+          <t>-22,57; 16,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,7; 20,94</t>
+          <t>-34,41; 20,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,11; 12,65</t>
+          <t>-35,68; 10,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,94; 220,81</t>
+          <t>-67,11; 250,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,15; 99,0</t>
+          <t>-59,02; 102,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,42; 140,66</t>
+          <t>-74,31; 138,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,15; 45,66</t>
+          <t>-70,57; 41,59</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-42,63; 20,8</t>
+          <t>-43,98; 19,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 32,11</t>
+          <t>-16,37; 28,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-41,62; 18,01</t>
+          <t>-43,92; 20,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-40,18; -1,59</t>
+          <t>-39,65; -0,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,02; 679,86</t>
+          <t>-50,28; 343,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-81,37; 194,21</t>
+          <t>-78,58; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-75,86; -5,43</t>
+          <t>-75,24; -1,05</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 46,57</t>
+          <t>-15,87; 48,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,97; 17,94</t>
+          <t>-28,15; 20,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 30,67</t>
+          <t>-20,53; 30,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 24,3</t>
+          <t>-34,41; 22,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,66; 200,36</t>
+          <t>-73,57; 223,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,85; 214,93</t>
+          <t>-52,0; 180,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,53; 131,42</t>
+          <t>-65,81; 104,64</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-42,83; 5,65</t>
+          <t>-43,43; 4,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-60,99; 6,3</t>
+          <t>-56,83; 6,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-61,99; 25,49</t>
+          <t>-61,51; 29,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-73,59; -0,45</t>
+          <t>-74,63; -1,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-83,83; 28,48</t>
+          <t>-83,86; 28,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-86,54; 108,6</t>
+          <t>-80,77; 104,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 3,4</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,73; 12,74</t>
+          <t>-48,54; 14,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-50,93; 6,57</t>
+          <t>-51,8; 9,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,04; 23,19</t>
+          <t>-35,49; 26,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,82; 6,63</t>
+          <t>-27,59; 7,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-83,33; 139,18</t>
+          <t>-84,53; 178,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-92,22; 100,73</t>
+          <t>-93,81; 105,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-70,48; 130,75</t>
+          <t>-68,43; 175,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-79,29; 57,45</t>
+          <t>-82,35; 63,23</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-27,91; 12,67</t>
+          <t>-25,3; 13,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-27,15; 15,51</t>
+          <t>-29,8; 14,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-36,25; 12,53</t>
+          <t>-32,65; 14,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 21,57</t>
+          <t>-13,56; 20,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-58,14; 49,46</t>
+          <t>-54,12; 63,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-61,59; 99,87</t>
+          <t>-62,68; 94,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-69,8; 70,6</t>
+          <t>-64,85; 101,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-37,57; 164,38</t>
+          <t>-36,81; 159,28</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-27,62; 11,69</t>
+          <t>-26,34; 11,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 25,61</t>
+          <t>-9,93; 24,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,34; 7,38</t>
+          <t>-32,74; 7,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-39,92; 1,94</t>
+          <t>-37,14; 3,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-72,2; 89,13</t>
+          <t>-69,06; 101,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,9; 359,61</t>
+          <t>-40,21; 316,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-76,06; 40,44</t>
+          <t>-76,21; 47,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-84,6; 14,45</t>
+          <t>-82,49; 36,71</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 1,92</t>
+          <t>-14,9; 2,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 2,97</t>
+          <t>-13,11; 3,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 0,05</t>
+          <t>-18,99; 0,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,67; -1,36</t>
+          <t>-18,38; -2,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 10,86</t>
+          <t>-47,18; 13,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 12,51</t>
+          <t>-37,91; 13,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-47,92; 0,31</t>
+          <t>-48,1; 2,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-49,23; -4,93</t>
+          <t>-47,82; -6,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P20B-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P20B-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,32</t>
+          <t>-4,87</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-30,81%</t>
+          <t>-26,56%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-55,67; -8,27</t>
+          <t>-63,29; -8,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-49,26; 4,54</t>
+          <t>-48,13; 3,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-46,21; 6,45</t>
+          <t>-45,7; 8,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-43,41; 15,02</t>
+          <t>-33,52; 15,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-72,87; 12,08</t>
+          <t>-73,41; 10,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-87,19; 56,03</t>
+          <t>-84,58; 73,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-90,98; —</t>
+          <t>-86,83; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-12,06</t>
+          <t>-13,97</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-30,74%</t>
+          <t>-34,21%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 16,4</t>
+          <t>-20,14; 17,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 16,21</t>
+          <t>-22,64; 14,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 20,52</t>
+          <t>-32,82; 17,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,68; 10,16</t>
+          <t>-35,5; 9,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,11; 250,28</t>
+          <t>-66,36; 264,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,02; 102,93</t>
+          <t>-59,96; 86,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-74,31; 138,0</t>
+          <t>-71,76; 128,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,57; 41,59</t>
+          <t>-69,88; 39,55</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-20,01</t>
+          <t>-19,34</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-49,1%</t>
+          <t>-48,05%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 19,41</t>
+          <t>-37,83; 19,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 28,48</t>
+          <t>-18,96; 27,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-43,92; 20,71</t>
+          <t>-42,75; 20,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-39,65; -0,5</t>
+          <t>-39,35; -0,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,28; 343,37</t>
+          <t>-54,46; 319,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-78,58; —</t>
+          <t>-78,58; 244,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-75,24; -1,05</t>
+          <t>-75,33; -1,11</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-6,54</t>
+          <t>-8,89</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-17,55%</t>
+          <t>-22,86%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 48,99</t>
+          <t>-16,0; 46,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,15; 20,31</t>
+          <t>-25,91; 17,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,53; 30,59</t>
+          <t>-19,38; 29,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 22,05</t>
+          <t>-36,3; 19,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,57; 223,49</t>
+          <t>-70,8; 203,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,0; 180,77</t>
+          <t>-50,07; 189,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,81; 104,64</t>
+          <t>-67,41; 92,81</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-39,32</t>
+          <t>-40,68</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-74,18%</t>
+          <t>-75,34%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-43,43; 4,17</t>
+          <t>-43,24; 4,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-56,83; 6,65</t>
+          <t>-59,55; 9,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-61,51; 29,3</t>
+          <t>-60,66; 27,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-74,63; -1,99</t>
+          <t>-77,29; -3,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-83,86; 28,62</t>
+          <t>-85,45; 36,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-80,77; 104,57</t>
+          <t>-82,61; 92,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 3,4</t>
+          <t>-94,56; 17,8</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-10,43</t>
+          <t>-10,3</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-40,66%</t>
+          <t>-40,94%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-48,54; 14,58</t>
+          <t>-49,09; 11,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,8; 9,63</t>
+          <t>-47,65; 9,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,49; 26,17</t>
+          <t>-35,28; 24,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 7,43</t>
+          <t>-27,8; 7,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-84,53; 178,44</t>
+          <t>-85,75; 121,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-93,81; 105,67</t>
+          <t>-91,25; 159,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-68,43; 175,22</t>
+          <t>-70,49; 146,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,35; 63,23</t>
+          <t>-81,54; 67,67</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,4</t>
+          <t>6,69</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-25,3; 13,6</t>
+          <t>-27,73; 14,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-29,8; 14,59</t>
+          <t>-27,73; 15,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-32,65; 14,68</t>
+          <t>-35,87; 13,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 20,7</t>
+          <t>-10,51; 21,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 63,82</t>
+          <t>-57,2; 65,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-62,68; 94,89</t>
+          <t>-62,23; 101,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-64,85; 101,9</t>
+          <t>-69,78; 81,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 159,28</t>
+          <t>-31,13; 147,91</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-16,82</t>
+          <t>-18,14</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-52,49%</t>
+          <t>-54,8%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-26,34; 11,41</t>
+          <t>-26,42; 13,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 24,12</t>
+          <t>-10,81; 25,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,74; 7,43</t>
+          <t>-32,95; 5,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,14; 3,58</t>
+          <t>-39,27; 1,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,06; 101,1</t>
+          <t>-70,83; 115,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,21; 316,64</t>
+          <t>-44,34; 394,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-76,21; 47,87</t>
+          <t>-76,94; 27,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-82,49; 36,71</t>
+          <t>-83,49; 12,08</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-10,13</t>
+          <t>-9,9</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-30,59%</t>
+          <t>-29,79%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 2,69</t>
+          <t>-14,99; 2,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 3,2</t>
+          <t>-13,55; 3,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 0,61</t>
+          <t>-18,67; -0,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,38; -2,41</t>
+          <t>-18,05; -1,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 13,67</t>
+          <t>-47,19; 14,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-37,91; 13,89</t>
+          <t>-39,16; 15,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 2,99</t>
+          <t>-46,47; -0,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-47,82; -6,54</t>
+          <t>-47,21; -3,06</t>
         </is>
       </c>
     </row>
